--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3685,7 +3685,7 @@
         <v>14045</v>
       </c>
       <c r="K64" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="65">
@@ -31675,7 +31675,7 @@
         <v>4461</v>
       </c>
       <c r="K64" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65">
@@ -46015,7 +46015,7 @@
         <v>43697</v>
       </c>
       <c r="K64" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -7270,7 +7270,7 @@
         <v>1817</v>
       </c>
       <c r="K64" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65">
@@ -42430,7 +42430,7 @@
         <v>2918</v>
       </c>
       <c r="K64" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="65">
@@ -46015,7 +46015,7 @@
         <v>43697</v>
       </c>
       <c r="K64" t="n">
-        <v>85</v>
+        <v>103</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3667,7 +3667,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E64" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F64" t="n">
         <v>156168</v>
@@ -3685,7 +3685,7 @@
         <v>14045</v>
       </c>
       <c r="K64" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="65">
@@ -7252,7 +7252,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -13867,7 +13867,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -17304,7 +17304,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -20902,7 +20902,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F64" t="n">
         <v>37421</v>
@@ -24487,7 +24487,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F64" t="n">
         <v>35588</v>
@@ -28072,7 +28072,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -31657,7 +31657,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F64" t="n">
         <v>52024</v>
@@ -35242,7 +35242,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F64" t="n">
         <v>30655</v>
@@ -38827,7 +38827,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -42412,7 +42412,7 @@
         <v>0.002124510646424138</v>
       </c>
       <c r="E64" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F64" t="n">
         <v>47895</v>
@@ -42430,7 +42430,7 @@
         <v>2918</v>
       </c>
       <c r="K64" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65">
@@ -45997,7 +45997,7 @@
         <v>0.02231940456400182</v>
       </c>
       <c r="E64" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F64" t="n">
         <v>390533</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3667,7 +3667,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E64" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F64" t="n">
         <v>156168</v>
@@ -7252,7 +7252,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -13867,7 +13867,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -17304,7 +17304,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -20902,7 +20902,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F64" t="n">
         <v>37421</v>
@@ -24487,7 +24487,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F64" t="n">
         <v>35588</v>
@@ -28072,7 +28072,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -31657,7 +31657,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F64" t="n">
         <v>52024</v>
@@ -35242,7 +35242,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F64" t="n">
         <v>30655</v>
@@ -38827,7 +38827,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -42412,7 +42412,7 @@
         <v>0.002124510646424138</v>
       </c>
       <c r="E64" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F64" t="n">
         <v>47895</v>
@@ -45997,7 +45997,7 @@
         <v>0.02231940456400182</v>
       </c>
       <c r="E64" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F64" t="n">
         <v>390533</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3667,7 +3667,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E64" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F64" t="n">
         <v>156168</v>
@@ -7252,7 +7252,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -13867,7 +13867,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -17304,7 +17304,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -20902,7 +20902,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F64" t="n">
         <v>37421</v>
@@ -24487,7 +24487,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F64" t="n">
         <v>35588</v>
@@ -28072,7 +28072,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -31657,7 +31657,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F64" t="n">
         <v>52024</v>
@@ -31672,10 +31672,10 @@
         <v>0.0323475399801056</v>
       </c>
       <c r="J64" t="n">
-        <v>4461</v>
+        <v>4479</v>
       </c>
       <c r="K64" t="n">
-        <v>102</v>
+        <v>84</v>
       </c>
     </row>
     <row r="65">
@@ -35242,7 +35242,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F64" t="n">
         <v>30655</v>
@@ -38827,7 +38827,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -42412,7 +42412,7 @@
         <v>0.002124510646424138</v>
       </c>
       <c r="E64" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F64" t="n">
         <v>47895</v>
@@ -45997,7 +45997,7 @@
         <v>0.02231940456400182</v>
       </c>
       <c r="E64" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F64" t="n">
         <v>390533</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3667,7 +3667,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E64" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F64" t="n">
         <v>156168</v>
@@ -7252,7 +7252,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -13867,7 +13867,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -17304,7 +17304,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -20902,7 +20902,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F64" t="n">
         <v>37421</v>
@@ -24487,7 +24487,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F64" t="n">
         <v>35588</v>
@@ -28072,7 +28072,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -31657,7 +31657,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F64" t="n">
         <v>52024</v>
@@ -35242,7 +35242,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F64" t="n">
         <v>30655</v>
@@ -38827,7 +38827,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -42412,7 +42412,7 @@
         <v>0.002124510646424138</v>
       </c>
       <c r="E64" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F64" t="n">
         <v>47895</v>
@@ -45997,7 +45997,7 @@
         <v>0.02231940456400182</v>
       </c>
       <c r="E64" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F64" t="n">
         <v>390533</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4000,7 +4000,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>156168</v>
@@ -7622,7 +7622,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -14274,7 +14274,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -17785,7 +17785,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -21420,7 +21420,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>37421</v>
@@ -25042,7 +25042,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>35588</v>
@@ -28664,7 +28664,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -32286,7 +32286,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>52024</v>
@@ -35908,7 +35908,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>30655</v>
@@ -39530,7 +39530,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -43152,7 +43152,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>47895</v>
@@ -46774,7 +46774,7 @@
         <v>0.02359561187819179</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>390533</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4000,7 +4000,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>156168</v>
@@ -7622,7 +7622,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -14274,7 +14274,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -17785,7 +17785,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -21420,7 +21420,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>37421</v>
@@ -25042,7 +25042,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>35588</v>
@@ -28664,7 +28664,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -32286,7 +32286,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>52024</v>
@@ -35908,7 +35908,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>30655</v>
@@ -39530,7 +39530,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -43152,7 +43152,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>47895</v>
@@ -46774,7 +46774,7 @@
         <v>0.02359561187819179</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>390533</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4000,7 +4000,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>156168</v>
@@ -7622,7 +7622,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -14274,7 +14274,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -17785,7 +17785,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -21420,7 +21420,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>37421</v>
@@ -25042,7 +25042,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>35588</v>
@@ -28664,7 +28664,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -32286,7 +32286,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>52024</v>
@@ -35908,7 +35908,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>30655</v>
@@ -39530,7 +39530,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -43152,7 +43152,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>47895</v>
@@ -46774,7 +46774,7 @@
         <v>0.02359561187819179</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>390533</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4000,7 +4000,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>156168</v>
@@ -7622,7 +7622,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -14274,7 +14274,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -17785,7 +17785,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -21420,7 +21420,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>37421</v>
@@ -25042,7 +25042,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>35588</v>
@@ -28664,7 +28664,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -32286,7 +32286,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>52024</v>
@@ -35908,7 +35908,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>30655</v>
@@ -39530,7 +39530,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -43152,7 +43152,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>47895</v>
@@ -46774,7 +46774,7 @@
         <v>0.02359561187819179</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>390533</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -21438,7 +21438,7 @@
         <v>3617</v>
       </c>
       <c r="K73" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4015,10 +4015,10 @@
         <v>0.01819581627671161</v>
       </c>
       <c r="J73" t="n">
-        <v>14045</v>
+        <v>14115</v>
       </c>
       <c r="K73" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -35923,10 +35923,10 @@
         <v>0.002152992986462241</v>
       </c>
       <c r="J73" t="n">
-        <v>1648</v>
+        <v>1717</v>
       </c>
       <c r="K73" t="n">
-        <v>69</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -46765,13 +46765,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>541175</v>
+        <v>541897</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>6373</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.02359561187819179</v>
+        <v>0.03701532059769246</v>
       </c>
       <c r="E73" t="n">
         <v>6</v>
@@ -46792,7 +46792,7 @@
         <v>43760</v>
       </c>
       <c r="K73" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74">
@@ -46808,7 +46808,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.1869894211669053</v>
+        <v>-0.1975103507395991</v>
       </c>
       <c r="E74" t="n">
         <v>15</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4000,7 +4000,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>156168</v>
@@ -7622,7 +7622,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -7640,7 +7640,7 @@
         <v>1817</v>
       </c>
       <c r="K73" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="74">
@@ -11244,7 +11244,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -14274,7 +14274,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -17785,7 +17785,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -21420,7 +21420,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>37421</v>
@@ -25042,7 +25042,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>35588</v>
@@ -28664,7 +28664,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -32286,7 +32286,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>52024</v>
@@ -35908,7 +35908,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>30655</v>
@@ -35926,7 +35926,7 @@
         <v>1717</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -39530,7 +39530,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -43152,7 +43152,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>47895</v>
@@ -46774,7 +46774,7 @@
         <v>0.03701532059769246</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>390533</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4000,7 +4000,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>156168</v>
@@ -4018,7 +4018,7 @@
         <v>14115</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -7622,7 +7622,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -14274,7 +14274,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -17785,7 +17785,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -21420,7 +21420,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>37421</v>
@@ -25042,7 +25042,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>35588</v>
@@ -28664,7 +28664,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -32286,7 +32286,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>52024</v>
@@ -35908,7 +35908,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>30655</v>
@@ -39530,7 +39530,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -43152,7 +43152,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>47895</v>
@@ -46774,7 +46774,7 @@
         <v>0.03701532059769246</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>390533</v>
@@ -46792,7 +46792,7 @@
         <v>43760</v>
       </c>
       <c r="K73" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4018,7 +4018,7 @@
         <v>14115</v>
       </c>
       <c r="K73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -21438,7 +21438,7 @@
         <v>3617</v>
       </c>
       <c r="K73" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74">
@@ -46792,7 +46792,7 @@
         <v>43760</v>
       </c>
       <c r="K73" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -32304,7 +32304,7 @@
         <v>4479</v>
       </c>
       <c r="K73" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="74">
@@ -39548,7 +39548,7 @@
         <v>3619</v>
       </c>
       <c r="K73" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="74">
@@ -46792,7 +46792,7 @@
         <v>43760</v>
       </c>
       <c r="K73" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4018,7 +4018,7 @@
         <v>14115</v>
       </c>
       <c r="K73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74">
@@ -46792,7 +46792,7 @@
         <v>43760</v>
       </c>
       <c r="K73" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4018,7 +4018,7 @@
         <v>14115</v>
       </c>
       <c r="K73" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74">
@@ -46792,7 +46792,7 @@
         <v>43760</v>
       </c>
       <c r="K73" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -32304,7 +32304,7 @@
         <v>4479</v>
       </c>
       <c r="K73" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="74">
@@ -39548,7 +39548,7 @@
         <v>3619</v>
       </c>
       <c r="K73" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="74">
@@ -46792,7 +46792,7 @@
         <v>43760</v>
       </c>
       <c r="K73" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4000,7 +4000,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>156168</v>
@@ -7622,7 +7622,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -14274,7 +14274,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -17785,7 +17785,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -21420,7 +21420,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>37421</v>
@@ -21435,10 +21435,10 @@
         <v>0.1218518856725413</v>
       </c>
       <c r="J73" t="n">
-        <v>3617</v>
+        <v>3688</v>
       </c>
       <c r="K73" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -25042,7 +25042,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>35588</v>
@@ -25057,10 +25057,10 @@
         <v>-0.02618396534617526</v>
       </c>
       <c r="J73" t="n">
-        <v>2554</v>
+        <v>2620</v>
       </c>
       <c r="K73" t="n">
-        <v>67</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -28664,7 +28664,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -32286,7 +32286,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>52024</v>
@@ -32301,10 +32301,10 @@
         <v>0.0323475399801056</v>
       </c>
       <c r="J73" t="n">
-        <v>4479</v>
+        <v>4566</v>
       </c>
       <c r="K73" t="n">
-        <v>86</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -35908,7 +35908,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>30655</v>
@@ -39530,7 +39530,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -39545,10 +39545,10 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>3619</v>
+        <v>3664</v>
       </c>
       <c r="K73" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -43152,7 +43152,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>47895</v>
@@ -43167,10 +43167,10 @@
         <v>0.001783307413167444</v>
       </c>
       <c r="J73" t="n">
-        <v>2918</v>
+        <v>2976</v>
       </c>
       <c r="K73" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -46774,7 +46774,7 @@
         <v>0.03701532059769246</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>390533</v>
@@ -46792,7 +46792,7 @@
         <v>43760</v>
       </c>
       <c r="K73" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4000,7 +4000,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F73" t="n">
         <v>156168</v>
@@ -4018,7 +4018,7 @@
         <v>14115</v>
       </c>
       <c r="K73" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74">
@@ -7622,7 +7622,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -14274,7 +14274,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -17785,7 +17785,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -21420,7 +21420,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F73" t="n">
         <v>37421</v>
@@ -25042,7 +25042,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F73" t="n">
         <v>35588</v>
@@ -28664,7 +28664,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -32286,7 +32286,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F73" t="n">
         <v>52024</v>
@@ -32304,7 +32304,7 @@
         <v>4566</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -35908,7 +35908,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F73" t="n">
         <v>30655</v>
@@ -39530,7 +39530,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -43152,7 +43152,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F73" t="n">
         <v>47895</v>
@@ -43170,7 +43170,7 @@
         <v>2976</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
@@ -46774,7 +46774,7 @@
         <v>0.03701532059769246</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F73" t="n">
         <v>390533</v>
@@ -46792,7 +46792,7 @@
         <v>43760</v>
       </c>
       <c r="K73" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4000,7 +4000,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E73" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F73" t="n">
         <v>156168</v>
@@ -4018,7 +4018,7 @@
         <v>14115</v>
       </c>
       <c r="K73" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="74">
@@ -7622,7 +7622,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -14274,7 +14274,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -17785,7 +17785,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -21420,7 +21420,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F73" t="n">
         <v>37421</v>
@@ -25042,7 +25042,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F73" t="n">
         <v>35588</v>
@@ -28664,7 +28664,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -32286,7 +32286,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F73" t="n">
         <v>52024</v>
@@ -35908,7 +35908,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F73" t="n">
         <v>30655</v>
@@ -39530,7 +39530,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -39548,7 +39548,7 @@
         <v>3664</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -43152,7 +43152,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F73" t="n">
         <v>47895</v>
@@ -43170,7 +43170,7 @@
         <v>2976</v>
       </c>
       <c r="K73" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74">
@@ -46774,7 +46774,7 @@
         <v>0.03701532059769246</v>
       </c>
       <c r="E73" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F73" t="n">
         <v>390533</v>
@@ -46792,7 +46792,7 @@
         <v>43760</v>
       </c>
       <c r="K73" t="n">
-        <v>92</v>
+        <v>123</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4018,7 +4018,7 @@
         <v>14115</v>
       </c>
       <c r="K73" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="74">
@@ -43170,7 +43170,7 @@
         <v>2976</v>
       </c>
       <c r="K73" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74">
@@ -46792,7 +46792,7 @@
         <v>43760</v>
       </c>
       <c r="K73" t="n">
-        <v>123</v>
+        <v>151</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4000,7 +4000,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E73" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F73" t="n">
         <v>156168</v>
@@ -4018,7 +4018,7 @@
         <v>14115</v>
       </c>
       <c r="K73" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="74">
@@ -7622,7 +7622,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -14274,7 +14274,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -17785,7 +17785,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -21420,7 +21420,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F73" t="n">
         <v>37421</v>
@@ -25042,7 +25042,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F73" t="n">
         <v>35588</v>
@@ -28664,7 +28664,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -32286,7 +32286,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F73" t="n">
         <v>52024</v>
@@ -32304,7 +32304,7 @@
         <v>4566</v>
       </c>
       <c r="K73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
@@ -35908,7 +35908,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F73" t="n">
         <v>30655</v>
@@ -39530,7 +39530,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -43152,7 +43152,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F73" t="n">
         <v>47895</v>
@@ -43170,7 +43170,7 @@
         <v>2976</v>
       </c>
       <c r="K73" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74">
@@ -46774,7 +46774,7 @@
         <v>0.03701532059769246</v>
       </c>
       <c r="E73" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F73" t="n">
         <v>390533</v>
@@ -46792,7 +46792,7 @@
         <v>43760</v>
       </c>
       <c r="K73" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4000,7 +4000,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E73" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F73" t="n">
         <v>156168</v>
@@ -4018,7 +4018,7 @@
         <v>14115</v>
       </c>
       <c r="K73" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="74">
@@ -7622,7 +7622,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -14274,7 +14274,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -17785,7 +17785,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -21420,7 +21420,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F73" t="n">
         <v>37421</v>
@@ -25042,7 +25042,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F73" t="n">
         <v>35588</v>
@@ -28664,7 +28664,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -32286,7 +32286,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F73" t="n">
         <v>52024</v>
@@ -32304,7 +32304,7 @@
         <v>4566</v>
       </c>
       <c r="K73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
@@ -35908,7 +35908,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F73" t="n">
         <v>30655</v>
@@ -39530,7 +39530,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -43152,7 +43152,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F73" t="n">
         <v>47895</v>
@@ -43170,7 +43170,7 @@
         <v>2976</v>
       </c>
       <c r="K73" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="74">
@@ -46774,7 +46774,7 @@
         <v>0.03701532059769246</v>
       </c>
       <c r="E73" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F73" t="n">
         <v>390533</v>
@@ -46792,7 +46792,7 @@
         <v>43760</v>
       </c>
       <c r="K73" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4000,7 +4000,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E73" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F73" t="n">
         <v>156168</v>
@@ -4018,7 +4018,7 @@
         <v>14115</v>
       </c>
       <c r="K73" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="74">
@@ -7622,7 +7622,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -14274,7 +14274,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -17785,7 +17785,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -21420,7 +21420,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F73" t="n">
         <v>37421</v>
@@ -25042,7 +25042,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F73" t="n">
         <v>35588</v>
@@ -28664,7 +28664,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -32286,7 +32286,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F73" t="n">
         <v>52024</v>
@@ -35908,7 +35908,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F73" t="n">
         <v>30655</v>
@@ -39530,7 +39530,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -43152,7 +43152,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F73" t="n">
         <v>47895</v>
@@ -43170,7 +43170,7 @@
         <v>2976</v>
       </c>
       <c r="K73" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74">
@@ -46774,7 +46774,7 @@
         <v>0.03701532059769246</v>
       </c>
       <c r="E73" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F73" t="n">
         <v>390533</v>
@@ -46792,7 +46792,7 @@
         <v>43760</v>
       </c>
       <c r="K73" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4000,7 +4000,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E73" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F73" t="n">
         <v>156168</v>
@@ -4018,7 +4018,7 @@
         <v>14115</v>
       </c>
       <c r="K73" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74">
@@ -7622,7 +7622,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -14274,7 +14274,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -17785,7 +17785,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -21420,7 +21420,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F73" t="n">
         <v>37421</v>
@@ -25042,7 +25042,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F73" t="n">
         <v>35588</v>
@@ -28664,7 +28664,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -32286,7 +32286,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F73" t="n">
         <v>52024</v>
@@ -35908,7 +35908,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F73" t="n">
         <v>30655</v>
@@ -39530,7 +39530,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -43152,7 +43152,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F73" t="n">
         <v>47895</v>
@@ -43170,7 +43170,7 @@
         <v>2976</v>
       </c>
       <c r="K73" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74">
@@ -46774,7 +46774,7 @@
         <v>0.03701532059769246</v>
       </c>
       <c r="E73" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F73" t="n">
         <v>390533</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4000,7 +4000,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E73" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F73" t="n">
         <v>156168</v>
@@ -7622,7 +7622,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -14274,7 +14274,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -17785,7 +17785,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -21420,7 +21420,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F73" t="n">
         <v>37421</v>
@@ -25042,7 +25042,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F73" t="n">
         <v>35588</v>
@@ -28664,7 +28664,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -32286,7 +32286,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F73" t="n">
         <v>52024</v>
@@ -35908,7 +35908,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F73" t="n">
         <v>30655</v>
@@ -39530,7 +39530,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -43152,7 +43152,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F73" t="n">
         <v>47895</v>
@@ -46774,7 +46774,7 @@
         <v>0.03701532059769246</v>
       </c>
       <c r="E73" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F73" t="n">
         <v>390533</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4000,7 +4000,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E73" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F73" t="n">
         <v>156168</v>
@@ -7622,7 +7622,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -14274,7 +14274,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -17785,7 +17785,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -21420,7 +21420,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F73" t="n">
         <v>37421</v>
@@ -25042,7 +25042,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F73" t="n">
         <v>35588</v>
@@ -28664,7 +28664,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -32286,7 +32286,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F73" t="n">
         <v>52024</v>
@@ -35908,7 +35908,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F73" t="n">
         <v>30655</v>
@@ -39530,7 +39530,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -43152,7 +43152,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F73" t="n">
         <v>47895</v>
@@ -46774,7 +46774,7 @@
         <v>0.03701532059769246</v>
       </c>
       <c r="E73" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F73" t="n">
         <v>390533</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4000,7 +4000,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E73" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F73" t="n">
         <v>156168</v>
@@ -7622,7 +7622,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -14274,7 +14274,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -17785,7 +17785,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -21420,7 +21420,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F73" t="n">
         <v>37421</v>
@@ -25042,7 +25042,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F73" t="n">
         <v>35588</v>
@@ -28664,7 +28664,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -32286,7 +32286,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F73" t="n">
         <v>52024</v>
@@ -35908,7 +35908,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F73" t="n">
         <v>30655</v>
@@ -39530,7 +39530,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -43152,7 +43152,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F73" t="n">
         <v>47895</v>
@@ -46774,7 +46774,7 @@
         <v>0.03701532059769246</v>
       </c>
       <c r="E73" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F73" t="n">
         <v>390533</v>
@@ -46789,10 +46789,10 @@
         <v>0.003546804701420838</v>
       </c>
       <c r="J73" t="n">
-        <v>43760</v>
+        <v>43810</v>
       </c>
       <c r="K73" t="n">
-        <v>165</v>
+        <v>115</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -1284,7 +1284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4320,60 +4320,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>165296</v>
+        <v>225704</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.2226230171234004</v>
+        <v>0.0614721139239911</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>44457</v>
+        <v>156168</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>6501</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.7217298231118789</v>
+        <v>0.01819581627671161</v>
       </c>
       <c r="J82" t="n">
-        <v>8088</v>
+        <v>14115</v>
       </c>
       <c r="K82" t="n">
-        <v>3133</v>
+        <v>50</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>175623</v>
+        <v>165296</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.06247580098731972</v>
+        <v>-0.2676425761173927</v>
       </c>
       <c r="E83" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F83" t="n">
-        <v>75066</v>
+        <v>44457</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -4382,13 +4382,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.6885079964909913</v>
+        <v>-0.7267026907400919</v>
       </c>
       <c r="J83" t="n">
-        <v>11291</v>
+        <v>8088</v>
       </c>
       <c r="K83" t="n">
-        <v>353</v>
+        <v>3133</v>
       </c>
     </row>
     <row r="84">
@@ -4404,7 +4404,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.06247580098731972</v>
       </c>
       <c r="E84" t="n">
         <v>27</v>
@@ -4419,7 +4419,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>0.6885079964909913</v>
       </c>
       <c r="J84" t="n">
         <v>11291</v>
@@ -4431,23 +4431,23 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>184255</v>
+        <v>175623</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.04915073765964595</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F85" t="n">
-        <v>79342</v>
+        <v>75066</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -4456,35 +4456,35 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.0569632057123065</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>11981</v>
+        <v>11291</v>
       </c>
       <c r="K85" t="n">
-        <v>55</v>
+        <v>353</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>185618</v>
+        <v>184255</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.00739735692382839</v>
+        <v>0.04915073765964595</v>
       </c>
       <c r="E86" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F86" t="n">
-        <v>82200</v>
+        <v>79342</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -4493,32 +4493,32 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.03602127498676615</v>
+        <v>0.0569632057123065</v>
       </c>
       <c r="J86" t="n">
-        <v>12308</v>
+        <v>11981</v>
       </c>
       <c r="K86" t="n">
-        <v>142</v>
+        <v>55</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>187160</v>
+        <v>185618</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.008307383982156902</v>
+        <v>0.00739735692382839</v>
       </c>
       <c r="E87" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F87" t="n">
         <v>82200</v>
@@ -4530,35 +4530,35 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0</v>
+        <v>0.03602127498676615</v>
       </c>
       <c r="J87" t="n">
-        <v>12199</v>
+        <v>12308</v>
       </c>
       <c r="K87" t="n">
-        <v>593</v>
+        <v>142</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>189413</v>
+        <v>187160</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.01203782859585381</v>
+        <v>0.008307383982156902</v>
       </c>
       <c r="E88" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F88" t="n">
-        <v>156777</v>
+        <v>82200</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -4567,109 +4567,109 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.9072627737226278</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>13187</v>
+        <v>12199</v>
       </c>
       <c r="K88" t="n">
-        <v>114</v>
+        <v>593</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>212633</v>
+        <v>189413</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.1225892626166103</v>
+        <v>0.01203782859585381</v>
       </c>
       <c r="E89" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="F89" t="n">
-        <v>155971</v>
+        <v>156777</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>6504</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.03634461687619996</v>
+        <v>0.9072627737226278</v>
       </c>
       <c r="J89" t="n">
-        <v>13677</v>
+        <v>13187</v>
       </c>
       <c r="K89" t="n">
-        <v>134</v>
+        <v>114</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>165296</v>
+        <v>212633</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.2226230171234004</v>
+        <v>0.1225892626166103</v>
       </c>
       <c r="E90" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F90" t="n">
-        <v>44457</v>
+        <v>155971</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>6504</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.7263763655947069</v>
+        <v>0.03634461687619996</v>
       </c>
       <c r="J90" t="n">
-        <v>8088</v>
+        <v>13677</v>
       </c>
       <c r="K90" t="n">
-        <v>3133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>175623</v>
+        <v>165296</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.06247580098731972</v>
+        <v>-0.2226230171234004</v>
       </c>
       <c r="E91" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F91" t="n">
-        <v>75066</v>
+        <v>44457</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -4678,35 +4678,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.6885079964909913</v>
+        <v>-0.7263763655947069</v>
       </c>
       <c r="J91" t="n">
-        <v>11291</v>
+        <v>8088</v>
       </c>
       <c r="K91" t="n">
-        <v>382</v>
+        <v>3133</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>184255</v>
+        <v>175623</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.04915073765964595</v>
+        <v>0.06247580098731972</v>
       </c>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F92" t="n">
-        <v>79342</v>
+        <v>75066</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -4715,35 +4715,35 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.0569632057123065</v>
+        <v>0.6885079964909913</v>
       </c>
       <c r="J92" t="n">
-        <v>11981</v>
+        <v>11291</v>
       </c>
       <c r="K92" t="n">
-        <v>89</v>
+        <v>382</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>185618</v>
+        <v>184255</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.00739735692382839</v>
+        <v>0.04915073765964595</v>
       </c>
       <c r="E93" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F93" t="n">
-        <v>82200</v>
+        <v>79342</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -4752,32 +4752,32 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.03602127498676615</v>
+        <v>0.0569632057123065</v>
       </c>
       <c r="J93" t="n">
-        <v>12282</v>
+        <v>11981</v>
       </c>
       <c r="K93" t="n">
-        <v>156</v>
+        <v>89</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>187160</v>
+        <v>185618</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.008307383982156902</v>
+        <v>0.00739735692382839</v>
       </c>
       <c r="E94" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F94" t="n">
         <v>82200</v>
@@ -4789,35 +4789,35 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0</v>
+        <v>0.03602127498676615</v>
       </c>
       <c r="J94" t="n">
-        <v>12199</v>
+        <v>12282</v>
       </c>
       <c r="K94" t="n">
-        <v>623</v>
+        <v>156</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>189413</v>
+        <v>187160</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.01203782859585381</v>
+        <v>0.008307383982156902</v>
       </c>
       <c r="E95" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F95" t="n">
-        <v>156777</v>
+        <v>82200</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -4826,71 +4826,108 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.9072627737226278</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>13337</v>
+        <v>12199</v>
       </c>
       <c r="K95" t="n">
-        <v>2</v>
+        <v>623</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>189413</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.01203782859585381</v>
+      </c>
+      <c r="E96" t="n">
+        <v>23</v>
+      </c>
+      <c r="F96" t="n">
+        <v>156777</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0.9072627737226278</v>
+      </c>
+      <c r="J96" t="n">
+        <v>13337</v>
+      </c>
+      <c r="K96" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>212633</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.1225892626166103</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>68</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>155971</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>6504</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.03634461687619996</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>13677</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>168</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>47337</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>111514</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>6504</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>5589</v>
       </c>
     </row>
@@ -4906,7 +4943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7942,20 +7979,20 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>19460</v>
+        <v>22522</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.1359559541781369</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -7970,29 +8007,29 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>739</v>
+        <v>1817</v>
       </c>
       <c r="K82" t="n">
-        <v>978</v>
+        <v>63</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>21933</v>
+        <v>19460</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.1270811921891059</v>
+        <v>-0.1359559541781369</v>
       </c>
       <c r="E83" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -8007,10 +8044,10 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>1743</v>
+        <v>739</v>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>978</v>
       </c>
     </row>
     <row r="84">
@@ -8026,7 +8063,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.1270811921891059</v>
       </c>
       <c r="E84" t="n">
         <v>27</v>
@@ -8053,20 +8090,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>22060</v>
+        <v>21933</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.005790361555646742</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -8081,7 +8118,7 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>1754</v>
+        <v>1743</v>
       </c>
       <c r="K85" t="n">
         <v>1</v>
@@ -8090,7 +8127,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -8100,10 +8137,10 @@
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0</v>
+        <v>0.005790361555646742</v>
       </c>
       <c r="E86" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -8118,29 +8155,29 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>1747</v>
+        <v>1754</v>
       </c>
       <c r="K86" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>21933</v>
+        <v>22060</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-0.005757026291931097</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -8158,26 +8195,26 @@
         <v>1747</v>
       </c>
       <c r="K87" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>22522</v>
+        <v>21933</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.02685451146673962</v>
+        <v>-0.005757026291931097</v>
       </c>
       <c r="E88" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -8192,16 +8229,16 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>1817</v>
+        <v>1747</v>
       </c>
       <c r="K88" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -8211,10 +8248,10 @@
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0</v>
+        <v>0.02685451146673962</v>
       </c>
       <c r="E89" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -8232,26 +8269,26 @@
         <v>1817</v>
       </c>
       <c r="K89" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>19460</v>
+        <v>22522</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.1359559541781369</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -8266,29 +8303,29 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>739</v>
+        <v>1817</v>
       </c>
       <c r="K90" t="n">
-        <v>978</v>
+        <v>34</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>21933</v>
+        <v>19460</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.1270811921891059</v>
+        <v>-0.1359559541781369</v>
       </c>
       <c r="E91" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -8303,29 +8340,29 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>1743</v>
+        <v>739</v>
       </c>
       <c r="K91" t="n">
-        <v>2</v>
+        <v>978</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>22060</v>
+        <v>21933</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.005790361555646742</v>
+        <v>0.1270811921891059</v>
       </c>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -8340,16 +8377,16 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>1754</v>
+        <v>1743</v>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -8359,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0</v>
+        <v>0.005790361555646742</v>
       </c>
       <c r="E93" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -8377,29 +8414,29 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>1747</v>
+        <v>1754</v>
       </c>
       <c r="K93" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>21933</v>
+        <v>22060</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>-0.005757026291931097</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -8417,26 +8454,26 @@
         <v>1747</v>
       </c>
       <c r="K94" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>22522</v>
+        <v>21933</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.02685451146673962</v>
+        <v>-0.005757026291931097</v>
       </c>
       <c r="E95" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -8451,16 +8488,16 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>1817</v>
+        <v>1747</v>
       </c>
       <c r="K95" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -8470,10 +8507,10 @@
         <v>0</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0</v>
+        <v>0.02685451146673962</v>
       </c>
       <c r="E96" t="n">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -8491,28 +8528,65 @@
         <v>1817</v>
       </c>
       <c r="K96" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>22522</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>68</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1817</v>
+      </c>
+      <c r="K97" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>3062</v>
       </c>
-      <c r="F97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="F98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>1078</v>
       </c>
     </row>
@@ -8528,7 +8602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11564,7 +11638,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -11577,7 +11651,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -11592,16 +11666,16 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="K82" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -11614,7 +11688,7 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -11629,10 +11703,10 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>73</v>
+        <v>218</v>
       </c>
       <c r="K83" t="n">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84">
@@ -11675,7 +11749,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -11688,7 +11762,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -11703,16 +11777,16 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -11725,7 +11799,7 @@
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -11749,7 +11823,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -11762,7 +11836,7 @@
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -11780,13 +11854,13 @@
         <v>80</v>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -11799,7 +11873,7 @@
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -11814,16 +11888,16 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -11836,7 +11910,7 @@
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -11860,7 +11934,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -11873,7 +11947,7 @@
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -11888,16 +11962,16 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="K90" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -11910,7 +11984,7 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -11925,16 +11999,16 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>73</v>
+        <v>218</v>
       </c>
       <c r="K91" t="n">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -11947,7 +12021,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -11962,16 +12036,16 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -11984,7 +12058,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -12008,7 +12082,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -12021,7 +12095,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -12039,13 +12113,13 @@
         <v>80</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -12058,7 +12132,7 @@
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -12073,16 +12147,16 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -12095,7 +12169,7 @@
         <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -12117,24 +12191,61 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1403</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>68</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>81</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="B98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>36</v>
       </c>
     </row>
@@ -12150,7 +12261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -14557,20 +14668,20 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>6106</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -14585,10 +14696,10 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66">
@@ -14604,7 +14715,7 @@
         <v>0</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E66" t="n">
         <v>27</v>
@@ -14631,11 +14742,11 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>6106</v>
+        <v>0</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -14644,7 +14755,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -14659,7 +14770,7 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -14668,7 +14779,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -14681,7 +14792,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -14699,13 +14810,13 @@
         <v>227</v>
       </c>
       <c r="K68" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -14718,7 +14829,7 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -14736,13 +14847,13 @@
         <v>227</v>
       </c>
       <c r="K69" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -14755,7 +14866,7 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -14770,16 +14881,16 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -14792,7 +14903,7 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -14810,26 +14921,26 @@
         <v>241</v>
       </c>
       <c r="K71" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0</v>
+        <v>6106</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -14844,29 +14955,29 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>6106</v>
+        <v>0</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -14881,16 +14992,16 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -14903,7 +15014,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -14921,13 +15032,13 @@
         <v>227</v>
       </c>
       <c r="K74" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -14940,7 +15051,7 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -14958,13 +15069,13 @@
         <v>227</v>
       </c>
       <c r="K75" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -14977,7 +15088,7 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -14992,16 +15103,16 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="K76" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -15014,7 +15125,7 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -15032,28 +15143,65 @@
         <v>241</v>
       </c>
       <c r="K77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>6106</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>68</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>241</v>
+      </c>
+      <c r="K78" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B78" s="4" t="n">
+      <c r="B79" s="4" t="n">
         <v>6106</v>
       </c>
-      <c r="F78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="4" t="n">
+      <c r="F79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4" t="n">
         <v>241</v>
       </c>
     </row>
@@ -15069,7 +15217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -18105,7 +18253,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -18118,7 +18266,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -18133,16 +18281,16 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>299</v>
+        <v>345</v>
       </c>
       <c r="K82" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -18155,7 +18303,7 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -18170,10 +18318,10 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="K83" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84">
@@ -18216,7 +18364,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -18229,7 +18377,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -18244,16 +18392,16 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>338</v>
+        <v>311</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -18266,7 +18414,7 @@
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -18284,13 +18432,13 @@
         <v>338</v>
       </c>
       <c r="K86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -18303,7 +18451,7 @@
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -18321,13 +18469,13 @@
         <v>338</v>
       </c>
       <c r="K87" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -18340,7 +18488,7 @@
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -18355,16 +18503,16 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="K88" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -18377,7 +18525,7 @@
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -18395,13 +18543,13 @@
         <v>345</v>
       </c>
       <c r="K89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -18414,7 +18562,7 @@
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -18429,16 +18577,16 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>299</v>
+        <v>345</v>
       </c>
       <c r="K90" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -18451,7 +18599,7 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -18466,16 +18614,16 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="K91" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -18488,7 +18636,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -18503,16 +18651,16 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>338</v>
+        <v>311</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -18525,7 +18673,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -18543,13 +18691,13 @@
         <v>338</v>
       </c>
       <c r="K93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -18562,7 +18710,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -18580,13 +18728,13 @@
         <v>338</v>
       </c>
       <c r="K94" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -18599,7 +18747,7 @@
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -18614,16 +18762,16 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="K95" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -18636,7 +18784,7 @@
         <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -18654,28 +18802,65 @@
         <v>345</v>
       </c>
       <c r="K96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>6526</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>68</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>345</v>
+      </c>
+      <c r="K97" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="B98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>46</v>
       </c>
     </row>
@@ -18704,7 +18889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -21740,60 +21925,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>47686</v>
+        <v>48707</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.02096207937257479</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>23083</v>
+        <v>37421</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>23919</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.5784311934983106</v>
+        <v>0.1218518856725413</v>
       </c>
       <c r="J82" t="n">
-        <v>673</v>
+        <v>3688</v>
       </c>
       <c r="K82" t="n">
-        <v>2568</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>48508</v>
+        <v>47686</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.01723776370423185</v>
+        <v>-0.02096207937257479</v>
       </c>
       <c r="E83" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F83" t="n">
-        <v>32355</v>
+        <v>23083</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -21802,13 +21987,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.4016808906987827</v>
+        <v>-0.6242206195972455</v>
       </c>
       <c r="J83" t="n">
-        <v>2998</v>
+        <v>673</v>
       </c>
       <c r="K83" t="n">
-        <v>383</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="84">
@@ -21824,7 +22009,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.01723776370423185</v>
       </c>
       <c r="E84" t="n">
         <v>27</v>
@@ -21839,7 +22024,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>0.4016808906987827</v>
       </c>
       <c r="J84" t="n">
         <v>2998</v>
@@ -21851,23 +22036,23 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>47907</v>
+        <v>48508</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>-0.01238970891399357</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F85" t="n">
-        <v>32135</v>
+        <v>32355</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -21876,19 +22061,19 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>-0.006799567300262711</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>3263</v>
+        <v>2998</v>
       </c>
       <c r="K85" t="n">
-        <v>107</v>
+        <v>383</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -21898,10 +22083,10 @@
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0</v>
+        <v>-0.01238970891399357</v>
       </c>
       <c r="E86" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F86" t="n">
         <v>32135</v>
@@ -21913,32 +22098,32 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0</v>
+        <v>-0.006799567300262711</v>
       </c>
       <c r="J86" t="n">
-        <v>3367</v>
+        <v>3263</v>
       </c>
       <c r="K86" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>48594</v>
+        <v>47907</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.01434028430083286</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F87" t="n">
         <v>32135</v>
@@ -21953,16 +22138,16 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>3566</v>
+        <v>3367</v>
       </c>
       <c r="K87" t="n">
-        <v>42</v>
+        <v>113</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -21972,13 +22157,13 @@
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>0.01434028430083286</v>
       </c>
       <c r="E88" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F88" t="n">
-        <v>36769</v>
+        <v>32135</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -21987,109 +22172,109 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.1442041387894819</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>3598</v>
+        <v>3566</v>
       </c>
       <c r="K88" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>48707</v>
+        <v>48594</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.002325389965839404</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="F89" t="n">
-        <v>37421</v>
+        <v>36769</v>
       </c>
       <c r="G89" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>17883</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.5064592455601186</v>
+        <v>0.1442041387894819</v>
       </c>
       <c r="J89" t="n">
-        <v>3618</v>
+        <v>3598</v>
       </c>
       <c r="K89" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>47686</v>
+        <v>48707</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.02096207937257479</v>
+        <v>0.002325389965839404</v>
       </c>
       <c r="E90" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F90" t="n">
-        <v>23083</v>
+        <v>37421</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>17883</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.5832716506291635</v>
+        <v>0.5064592455601186</v>
       </c>
       <c r="J90" t="n">
-        <v>673</v>
+        <v>3618</v>
       </c>
       <c r="K90" t="n">
-        <v>2568</v>
+        <v>38</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>48508</v>
+        <v>47686</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.01723776370423185</v>
+        <v>-0.02096207937257479</v>
       </c>
       <c r="E91" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F91" t="n">
-        <v>32355</v>
+        <v>23083</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -22098,35 +22283,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.4016808906987827</v>
+        <v>-0.5832716506291635</v>
       </c>
       <c r="J91" t="n">
-        <v>2998</v>
+        <v>673</v>
       </c>
       <c r="K91" t="n">
-        <v>385</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>47907</v>
+        <v>48508</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>-0.01238970891399357</v>
+        <v>0.01723776370423185</v>
       </c>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F92" t="n">
-        <v>32135</v>
+        <v>32355</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -22135,19 +22320,19 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>-0.006799567300262711</v>
+        <v>0.4016808906987827</v>
       </c>
       <c r="J92" t="n">
-        <v>3263</v>
+        <v>2998</v>
       </c>
       <c r="K92" t="n">
-        <v>109</v>
+        <v>385</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -22157,10 +22342,10 @@
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0</v>
+        <v>-0.01238970891399357</v>
       </c>
       <c r="E93" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F93" t="n">
         <v>32135</v>
@@ -22172,35 +22357,35 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0</v>
+        <v>-0.006799567300262711</v>
       </c>
       <c r="J93" t="n">
-        <v>3367</v>
+        <v>3263</v>
       </c>
       <c r="K93" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>48594</v>
+        <v>47907</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.01434028430083286</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F94" t="n">
-        <v>36769</v>
+        <v>32135</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -22209,19 +22394,19 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.1442041387894819</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>3566</v>
+        <v>3367</v>
       </c>
       <c r="K94" t="n">
-        <v>44</v>
+        <v>113</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -22231,10 +22416,10 @@
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0</v>
+        <v>0.01434028430083286</v>
       </c>
       <c r="E95" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F95" t="n">
         <v>36769</v>
@@ -22246,71 +22431,108 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0</v>
+        <v>0.1442041387894819</v>
       </c>
       <c r="J95" t="n">
-        <v>3598</v>
+        <v>3566</v>
       </c>
       <c r="K95" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>48594</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>23</v>
+      </c>
+      <c r="F96" t="n">
+        <v>36769</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>3598</v>
+      </c>
+      <c r="K96" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>48707</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.002325389965839404</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>68</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>37421</v>
       </c>
-      <c r="G96" t="n">
+      <c r="G97" t="n">
         <v>87</v>
       </c>
-      <c r="H96" t="n">
+      <c r="H97" t="n">
         <v>17883</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.5064592455601186</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>3618</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>42</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>1021</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>14338</v>
       </c>
-      <c r="G97" s="4" t="n">
+      <c r="G98" s="4" t="n">
         <v>87</v>
       </c>
-      <c r="H97" s="4" t="n">
+      <c r="H98" s="4" t="n">
         <v>17883</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>2945</v>
       </c>
     </row>
@@ -22326,7 +22548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -25362,60 +25584,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>33645</v>
+        <v>43207</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.2213067327053487</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>35588</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>4653</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-1</v>
+        <v>-0.02618396534617526</v>
       </c>
       <c r="J82" t="n">
-        <v>998</v>
+        <v>2620</v>
       </c>
       <c r="K82" t="n">
-        <v>1385</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>37373</v>
+        <v>33645</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.1108039827611829</v>
+        <v>-0.2213067327053487</v>
       </c>
       <c r="E83" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F83" t="n">
-        <v>6423</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -25424,13 +25646,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J83" t="n">
-        <v>2250</v>
+        <v>998</v>
       </c>
       <c r="K83" t="n">
-        <v>165</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="84">
@@ -25446,7 +25668,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.1108039827611829</v>
       </c>
       <c r="E84" t="n">
         <v>27</v>
@@ -25473,23 +25695,23 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>38864</v>
+        <v>37373</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.03989511144409066</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F85" t="n">
-        <v>6552</v>
+        <v>6423</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -25498,19 +25720,19 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.02008407286314806</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>2432</v>
+        <v>2250</v>
       </c>
       <c r="K85" t="n">
-        <v>12</v>
+        <v>165</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -25520,10 +25742,10 @@
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0</v>
+        <v>0.03989511144409066</v>
       </c>
       <c r="E86" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F86" t="n">
         <v>6552</v>
@@ -25535,32 +25757,32 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0</v>
+        <v>0.02008407286314806</v>
       </c>
       <c r="J86" t="n">
         <v>2432</v>
       </c>
       <c r="K86" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>39545</v>
+        <v>38864</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.01752264306298889</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F87" t="n">
         <v>6552</v>
@@ -25575,16 +25797,16 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>2485</v>
+        <v>2432</v>
       </c>
       <c r="K87" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -25594,13 +25816,13 @@
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>0.01752264306298889</v>
       </c>
       <c r="E88" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F88" t="n">
-        <v>41323</v>
+        <v>6552</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -25609,32 +25831,32 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>5.306929181929182</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>2555</v>
+        <v>2485</v>
       </c>
       <c r="K88" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>43207</v>
+        <v>39545</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.09260336325704893</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="F89" t="n">
         <v>41323</v>
@@ -25646,35 +25868,35 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0</v>
+        <v>5.306929181929182</v>
       </c>
       <c r="J89" t="n">
         <v>2555</v>
       </c>
       <c r="K89" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>33645</v>
+        <v>43207</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.2213067327053487</v>
+        <v>0.09260336325704893</v>
       </c>
       <c r="E90" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>41323</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -25683,35 +25905,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>998</v>
+        <v>2555</v>
       </c>
       <c r="K90" t="n">
-        <v>1385</v>
+        <v>43</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>37373</v>
+        <v>33645</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.1108039827611829</v>
+        <v>-0.2213067327053487</v>
       </c>
       <c r="E91" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F91" t="n">
-        <v>6423</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -25720,35 +25942,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J91" t="n">
-        <v>2250</v>
+        <v>998</v>
       </c>
       <c r="K91" t="n">
-        <v>166</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>38864</v>
+        <v>37373</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.03989511144409066</v>
+        <v>0.1108039827611829</v>
       </c>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F92" t="n">
-        <v>6552</v>
+        <v>6423</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -25757,19 +25979,19 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.02008407286314806</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>2432</v>
+        <v>2250</v>
       </c>
       <c r="K92" t="n">
-        <v>19</v>
+        <v>166</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -25779,10 +26001,10 @@
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0</v>
+        <v>0.03989511144409066</v>
       </c>
       <c r="E93" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F93" t="n">
         <v>6552</v>
@@ -25794,35 +26016,35 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0</v>
+        <v>0.02008407286314806</v>
       </c>
       <c r="J93" t="n">
         <v>2432</v>
       </c>
       <c r="K93" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>39545</v>
+        <v>38864</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.01752264306298889</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F94" t="n">
-        <v>29721</v>
+        <v>6552</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -25831,35 +26053,35 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>3.536172161172161</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>2485</v>
+        <v>2432</v>
       </c>
       <c r="K94" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>40472</v>
+        <v>39545</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.02344164875458338</v>
+        <v>0.01752264306298889</v>
       </c>
       <c r="E95" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F95" t="n">
-        <v>41323</v>
+        <v>29721</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -25868,32 +26090,32 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.3903637158911207</v>
+        <v>3.536172161172161</v>
       </c>
       <c r="J95" t="n">
-        <v>2555</v>
+        <v>2485</v>
       </c>
       <c r="K95" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>43207</v>
+        <v>40472</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0.06757758450286618</v>
+        <v>0.02344164875458338</v>
       </c>
       <c r="E96" t="n">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="F96" t="n">
         <v>41323</v>
@@ -25905,34 +26127,71 @@
         <v>0</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0</v>
+        <v>0.3903637158911207</v>
       </c>
       <c r="J96" t="n">
         <v>2555</v>
       </c>
       <c r="K96" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>43207</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0.06757758450286618</v>
+      </c>
+      <c r="E97" t="n">
+        <v>68</v>
+      </c>
+      <c r="F97" t="n">
+        <v>41323</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>2555</v>
+      </c>
+      <c r="K97" t="n">
         <v>47</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>9562</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>41323</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>1557</v>
       </c>
     </row>
@@ -25948,7 +26207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -28984,20 +29243,20 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3366</v>
+        <v>2396</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.4048414023372287</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -29012,16 +29271,16 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>218</v>
+        <v>178</v>
       </c>
       <c r="K82" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -29031,10 +29290,10 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0</v>
+        <v>0.4048414023372287</v>
       </c>
       <c r="E83" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -29049,10 +29308,10 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>155</v>
+        <v>218</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84">
@@ -29095,7 +29354,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -29108,7 +29367,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -29123,16 +29382,16 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="K85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -29145,7 +29404,7 @@
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -29160,29 +29419,29 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2260</v>
+        <v>3366</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-0.3285799168152109</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -29200,26 +29459,26 @@
         <v>156</v>
       </c>
       <c r="K87" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2396</v>
+        <v>2260</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.06017699115044248</v>
+        <v>-0.3285799168152109</v>
       </c>
       <c r="E88" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -29234,16 +29493,16 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="K88" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -29253,10 +29512,10 @@
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0</v>
+        <v>0.06017699115044248</v>
       </c>
       <c r="E89" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -29274,26 +29533,26 @@
         <v>178</v>
       </c>
       <c r="K89" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3366</v>
+        <v>2396</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.4048414023372287</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -29308,16 +29567,16 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>218</v>
+        <v>178</v>
       </c>
       <c r="K90" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -29327,10 +29586,10 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>0.4048414023372287</v>
       </c>
       <c r="E91" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -29345,16 +29604,16 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>155</v>
+        <v>218</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -29367,7 +29626,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -29382,16 +29641,16 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -29404,7 +29663,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -29428,20 +29687,20 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>2260</v>
+        <v>3366</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>-0.3285799168152109</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -29459,26 +29718,26 @@
         <v>156</v>
       </c>
       <c r="K94" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2396</v>
+        <v>2260</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.06017699115044248</v>
+        <v>-0.3285799168152109</v>
       </c>
       <c r="E95" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -29493,16 +29752,16 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="K95" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -29512,10 +29771,10 @@
         <v>0</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0</v>
+        <v>0.06017699115044248</v>
       </c>
       <c r="E96" t="n">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -29533,28 +29792,65 @@
         <v>178</v>
       </c>
       <c r="K96" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>2396</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>68</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>178</v>
+      </c>
+      <c r="K97" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>-970</v>
       </c>
-      <c r="F97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="F98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>61</v>
       </c>
     </row>
@@ -29570,7 +29866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -32606,44 +32902,44 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>56610</v>
+        <v>72396</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.2180507210343113</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>49596</v>
+        <v>52024</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>1943</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.05126635549774275</v>
+        <v>0.0323475399801056</v>
       </c>
       <c r="J82" t="n">
-        <v>3986</v>
+        <v>4566</v>
       </c>
       <c r="K82" t="n">
-        <v>281</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -32653,13 +32949,13 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0</v>
+        <v>-0.2180507210343113</v>
       </c>
       <c r="E83" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F83" t="n">
-        <v>49261</v>
+        <v>49596</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -32668,13 +32964,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>-0.006754576982014679</v>
+        <v>-0.08099394074156428</v>
       </c>
       <c r="J83" t="n">
-        <v>3898</v>
+        <v>3986</v>
       </c>
       <c r="K83" t="n">
-        <v>339</v>
+        <v>281</v>
       </c>
     </row>
     <row r="84">
@@ -32705,7 +33001,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>-0.006754576982014679</v>
       </c>
       <c r="J84" t="n">
         <v>3898</v>
@@ -32717,20 +33013,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>56164</v>
+        <v>56610</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>-0.007878466701996113</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F85" t="n">
         <v>49261</v>
@@ -32745,29 +33041,29 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>4195</v>
+        <v>3898</v>
       </c>
       <c r="K85" t="n">
-        <v>61</v>
+        <v>339</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>57028</v>
+        <v>56164</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.01538351969232961</v>
+        <v>-0.007878466701996113</v>
       </c>
       <c r="E86" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F86" t="n">
         <v>49261</v>
@@ -32785,29 +33081,29 @@
         <v>4195</v>
       </c>
       <c r="K86" t="n">
-        <v>92</v>
+        <v>61</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>63542</v>
+        <v>57028</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.1142245914287718</v>
+        <v>0.01538351969232961</v>
       </c>
       <c r="E87" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F87" t="n">
-        <v>51725</v>
+        <v>49261</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -32816,35 +33112,35 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.05001928503278456</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>4324</v>
+        <v>4195</v>
       </c>
       <c r="K87" t="n">
-        <v>25</v>
+        <v>92</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>63819</v>
+        <v>63542</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.004359321393723836</v>
+        <v>0.1142245914287718</v>
       </c>
       <c r="E88" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F88" t="n">
-        <v>52276</v>
+        <v>51725</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -32853,93 +33149,93 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.01065248912518125</v>
+        <v>0.05001928503278456</v>
       </c>
       <c r="J88" t="n">
-        <v>4384</v>
+        <v>4324</v>
       </c>
       <c r="K88" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>72396</v>
+        <v>63819</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.1343957128754759</v>
+        <v>0.004359321393723836</v>
       </c>
       <c r="E89" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="F89" t="n">
-        <v>52024</v>
+        <v>52276</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>1943</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.0323475399801056</v>
+        <v>0.01065248912518125</v>
       </c>
       <c r="J89" t="n">
-        <v>4462</v>
+        <v>4384</v>
       </c>
       <c r="K89" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>56610</v>
+        <v>72396</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.2180507210343113</v>
+        <v>0.1343957128754759</v>
       </c>
       <c r="E90" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F90" t="n">
-        <v>49596</v>
+        <v>52024</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>1943</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.08099394074156428</v>
+        <v>0.0323475399801056</v>
       </c>
       <c r="J90" t="n">
-        <v>3986</v>
+        <v>4462</v>
       </c>
       <c r="K90" t="n">
-        <v>281</v>
+        <v>33</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -32949,13 +33245,13 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-0.2180507210343113</v>
       </c>
       <c r="E91" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F91" t="n">
-        <v>49261</v>
+        <v>49596</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -32964,32 +33260,32 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-0.006754576982014679</v>
+        <v>-0.08099394074156428</v>
       </c>
       <c r="J91" t="n">
-        <v>3898</v>
+        <v>3986</v>
       </c>
       <c r="K91" t="n">
-        <v>345</v>
+        <v>281</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>56164</v>
+        <v>56610</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>-0.007878466701996113</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F92" t="n">
         <v>49261</v>
@@ -33001,32 +33297,32 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>-0.006754576982014679</v>
       </c>
       <c r="J92" t="n">
-        <v>4195</v>
+        <v>3898</v>
       </c>
       <c r="K92" t="n">
-        <v>61</v>
+        <v>345</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>57028</v>
+        <v>56164</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.01538351969232961</v>
+        <v>-0.007878466701996113</v>
       </c>
       <c r="E93" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F93" t="n">
         <v>49261</v>
@@ -33041,32 +33337,32 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>4241</v>
+        <v>4195</v>
       </c>
       <c r="K93" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>63542</v>
+        <v>57028</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.1142245914287718</v>
+        <v>0.01538351969232961</v>
       </c>
       <c r="E94" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F94" t="n">
-        <v>51725</v>
+        <v>49261</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -33075,35 +33371,35 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.05001928503278456</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>4324</v>
+        <v>4241</v>
       </c>
       <c r="K94" t="n">
-        <v>29</v>
+        <v>71</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>63819</v>
+        <v>63542</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.004359321393723836</v>
+        <v>0.1142245914287718</v>
       </c>
       <c r="E95" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F95" t="n">
-        <v>52276</v>
+        <v>51725</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -33112,71 +33408,108 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.01065248912518125</v>
+        <v>0.05001928503278456</v>
       </c>
       <c r="J95" t="n">
-        <v>4384</v>
+        <v>4324</v>
       </c>
       <c r="K95" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>63819</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.004359321393723836</v>
+      </c>
+      <c r="E96" t="n">
+        <v>23</v>
+      </c>
+      <c r="F96" t="n">
+        <v>52276</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0.01065248912518125</v>
+      </c>
+      <c r="J96" t="n">
+        <v>4384</v>
+      </c>
+      <c r="K96" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>72396</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.1343957128754759</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>68</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>52024</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>1943</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.0323475399801056</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>4462</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>15786</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>2428</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>1943</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>476</v>
       </c>
     </row>
@@ -33192,7 +33525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -36228,60 +36561,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>14675</v>
+        <v>28057</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.4769576219838186</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>30655</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-1</v>
+        <v>0.002152992986462241</v>
       </c>
       <c r="J82" t="n">
-        <v>1360</v>
+        <v>1717</v>
       </c>
       <c r="K82" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>22250</v>
+        <v>14675</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.5161839863713799</v>
+        <v>-0.4769576219838186</v>
       </c>
       <c r="E83" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F83" t="n">
-        <v>14470</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -36290,13 +36623,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J83" t="n">
-        <v>1415</v>
+        <v>1360</v>
       </c>
       <c r="K83" t="n">
-        <v>101</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84">
@@ -36312,7 +36645,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.5161839863713799</v>
       </c>
       <c r="E84" t="n">
         <v>27</v>
@@ -36339,20 +36672,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>23511</v>
+        <v>22250</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.05667415730337079</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F85" t="n">
         <v>14470</v>
@@ -36367,29 +36700,29 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>1538</v>
+        <v>1415</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>23754</v>
+        <v>23511</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.01033558759729488</v>
+        <v>0.05667415730337079</v>
       </c>
       <c r="E86" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F86" t="n">
         <v>14470</v>
@@ -36404,29 +36737,29 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>1579</v>
+        <v>1538</v>
       </c>
       <c r="K86" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>25290</v>
+        <v>23754</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.06466279363475626</v>
+        <v>0.01033558759729488</v>
       </c>
       <c r="E87" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F87" t="n">
         <v>14470</v>
@@ -36441,32 +36774,32 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>1618</v>
+        <v>1579</v>
       </c>
       <c r="K87" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>26728</v>
+        <v>25290</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.05686041913799921</v>
+        <v>0.06466279363475626</v>
       </c>
       <c r="E88" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F88" t="n">
-        <v>30655</v>
+        <v>14470</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -36475,32 +36808,32 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>1.118521078092605</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>1643</v>
+        <v>1618</v>
       </c>
       <c r="K88" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>28057</v>
+        <v>26728</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.04972313678539359</v>
+        <v>0.05686041913799921</v>
       </c>
       <c r="E89" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="F89" t="n">
         <v>30655</v>
@@ -36509,75 +36842,75 @@
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.002152992986462241</v>
+        <v>1.118521078092605</v>
       </c>
       <c r="J89" t="n">
-        <v>1649</v>
+        <v>1643</v>
       </c>
       <c r="K89" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>14675</v>
+        <v>28057</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.4769576219838186</v>
+        <v>0.04972313678539359</v>
       </c>
       <c r="E90" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>30655</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-1</v>
+        <v>0.002152992986462241</v>
       </c>
       <c r="J90" t="n">
-        <v>1360</v>
+        <v>1649</v>
       </c>
       <c r="K90" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>22250</v>
+        <v>14675</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.5161839863713799</v>
+        <v>-0.4769576219838186</v>
       </c>
       <c r="E91" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F91" t="n">
-        <v>14470</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -36586,32 +36919,32 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J91" t="n">
-        <v>1415</v>
+        <v>1360</v>
       </c>
       <c r="K91" t="n">
-        <v>101</v>
+        <v>46</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>23511</v>
+        <v>22250</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.05667415730337079</v>
+        <v>0.5161839863713799</v>
       </c>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F92" t="n">
         <v>14470</v>
@@ -36626,29 +36959,29 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>1538</v>
+        <v>1415</v>
       </c>
       <c r="K92" t="n">
-        <v>13</v>
+        <v>101</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>23754</v>
+        <v>23511</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.01033558759729488</v>
+        <v>0.05667415730337079</v>
       </c>
       <c r="E93" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F93" t="n">
         <v>14470</v>
@@ -36663,32 +36996,32 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>1579</v>
+        <v>1538</v>
       </c>
       <c r="K93" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>25290</v>
+        <v>23754</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.06466279363475626</v>
+        <v>0.01033558759729488</v>
       </c>
       <c r="E94" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F94" t="n">
-        <v>30655</v>
+        <v>14470</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -36697,32 +37030,32 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>1.118521078092605</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>1618</v>
+        <v>1579</v>
       </c>
       <c r="K94" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>26728</v>
+        <v>25290</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.05686041913799921</v>
+        <v>0.06466279363475626</v>
       </c>
       <c r="E95" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F95" t="n">
         <v>30655</v>
@@ -36734,32 +37067,32 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0</v>
+        <v>1.118521078092605</v>
       </c>
       <c r="J95" t="n">
-        <v>1643</v>
+        <v>1618</v>
       </c>
       <c r="K95" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>28057</v>
+        <v>26728</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0.04972313678539359</v>
+        <v>0.05686041913799921</v>
       </c>
       <c r="E96" t="n">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="F96" t="n">
         <v>30655</v>
@@ -36768,37 +37101,74 @@
         <v>0</v>
       </c>
       <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>1643</v>
+      </c>
+      <c r="K96" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>28057</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0.04972313678539359</v>
+      </c>
+      <c r="E97" t="n">
+        <v>68</v>
+      </c>
+      <c r="F97" t="n">
+        <v>30655</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>66</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.002152992986462241</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>1649</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>13382</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>30655</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>289</v>
       </c>
     </row>
@@ -36814,7 +37184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -39850,20 +40220,20 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>31914</v>
+        <v>36396</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.1231454005934718</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -39878,29 +40248,29 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>3397</v>
+        <v>3664</v>
       </c>
       <c r="K82" t="n">
-        <v>184</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>27276</v>
+        <v>31914</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.1453280691859372</v>
+        <v>-0.1231454005934718</v>
       </c>
       <c r="E83" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -39915,10 +40285,10 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>3632</v>
+        <v>3397</v>
       </c>
       <c r="K83" t="n">
-        <v>43</v>
+        <v>184</v>
       </c>
     </row>
     <row r="84">
@@ -39934,7 +40304,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>-0.1453280691859372</v>
       </c>
       <c r="E84" t="n">
         <v>27</v>
@@ -39961,7 +40331,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -39974,7 +40344,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -39989,16 +40359,16 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>3583</v>
+        <v>3632</v>
       </c>
       <c r="K85" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -40011,7 +40381,7 @@
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -40029,13 +40399,13 @@
         <v>3583</v>
       </c>
       <c r="K86" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -40048,7 +40418,7 @@
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -40063,29 +40433,29 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>3594</v>
+        <v>3583</v>
       </c>
       <c r="K87" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>36117</v>
+        <v>27276</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.3241311042674879</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -40100,29 +40470,29 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>3620</v>
+        <v>3594</v>
       </c>
       <c r="K88" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>36396</v>
+        <v>36117</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.00772489409419387</v>
+        <v>0.3241311042674879</v>
       </c>
       <c r="E89" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -40140,26 +40510,26 @@
         <v>3620</v>
       </c>
       <c r="K89" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>31914</v>
+        <v>36396</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.1231454005934718</v>
+        <v>0.00772489409419387</v>
       </c>
       <c r="E90" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -40174,29 +40544,29 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>3397</v>
+        <v>3620</v>
       </c>
       <c r="K90" t="n">
-        <v>184</v>
+        <v>24</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>27276</v>
+        <v>31914</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>-0.1453280691859372</v>
+        <v>-0.1231454005934718</v>
       </c>
       <c r="E91" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -40211,16 +40581,16 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>3632</v>
+        <v>3397</v>
       </c>
       <c r="K91" t="n">
-        <v>43</v>
+        <v>184</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -40230,10 +40600,10 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>-0.1453280691859372</v>
       </c>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -40248,16 +40618,16 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>3583</v>
+        <v>3632</v>
       </c>
       <c r="K92" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -40270,7 +40640,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -40285,16 +40655,16 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>3594</v>
+        <v>3583</v>
       </c>
       <c r="K93" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -40307,7 +40677,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -40325,26 +40695,26 @@
         <v>3594</v>
       </c>
       <c r="K94" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>36396</v>
+        <v>27276</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.3343598768147822</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -40359,16 +40729,16 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>3620</v>
+        <v>3594</v>
       </c>
       <c r="K95" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -40378,10 +40748,10 @@
         <v>0</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0</v>
+        <v>0.3343598768147822</v>
       </c>
       <c r="E96" t="n">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -40399,28 +40769,65 @@
         <v>3620</v>
       </c>
       <c r="K96" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>36396</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>68</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>3620</v>
+      </c>
+      <c r="K97" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>4482</v>
       </c>
-      <c r="F97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="F98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>223</v>
       </c>
     </row>
@@ -40436,7 +40843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -43472,60 +43879,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>36888</v>
+        <v>41981</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.12131678616517</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>35470</v>
+        <v>47895</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>416</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.2644893727319855</v>
+        <v>0.001783307413167444</v>
       </c>
       <c r="J82" t="n">
-        <v>1120</v>
+        <v>2976</v>
       </c>
       <c r="K82" t="n">
-        <v>1527</v>
+        <v>30</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>37192</v>
+        <v>36888</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.008241162437649101</v>
+        <v>-0.12131678616517</v>
       </c>
       <c r="E83" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F83" t="n">
-        <v>45049</v>
+        <v>35470</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -43534,13 +43941,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.2700592049619397</v>
+        <v>-0.265798679389787</v>
       </c>
       <c r="J83" t="n">
-        <v>2497</v>
+        <v>1120</v>
       </c>
       <c r="K83" t="n">
-        <v>176</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="84">
@@ -43556,7 +43963,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.008241162437649101</v>
       </c>
       <c r="E84" t="n">
         <v>27</v>
@@ -43571,7 +43978,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>0.2700592049619397</v>
       </c>
       <c r="J84" t="n">
         <v>2497</v>
@@ -43583,20 +43990,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>39627</v>
+        <v>37192</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.06547106904710691</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F85" t="n">
         <v>45049</v>
@@ -43611,29 +44018,29 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>2686</v>
+        <v>2497</v>
       </c>
       <c r="K85" t="n">
-        <v>32</v>
+        <v>176</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>39858</v>
+        <v>39627</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.005829358770535241</v>
+        <v>0.06547106904710691</v>
       </c>
       <c r="E86" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F86" t="n">
         <v>45049</v>
@@ -43648,29 +44055,29 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>2733</v>
+        <v>2686</v>
       </c>
       <c r="K86" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>41547</v>
+        <v>39858</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.04237543278639169</v>
+        <v>0.005829358770535241</v>
       </c>
       <c r="E87" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F87" t="n">
         <v>45049</v>
@@ -43685,16 +44092,16 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>2689</v>
+        <v>2733</v>
       </c>
       <c r="K87" t="n">
-        <v>124</v>
+        <v>36</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -43704,13 +44111,13 @@
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>0.04237543278639169</v>
       </c>
       <c r="E88" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F88" t="n">
-        <v>48225</v>
+        <v>45049</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -43719,109 +44126,109 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.070501010011321</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>2852</v>
+        <v>2689</v>
       </c>
       <c r="K88" t="n">
-        <v>12</v>
+        <v>124</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>41981</v>
+        <v>41547</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.01044600091462681</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="F89" t="n">
-        <v>47895</v>
+        <v>48225</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0</v>
+        <v>0.070501010011321</v>
       </c>
       <c r="J89" t="n">
-        <v>2919</v>
+        <v>2852</v>
       </c>
       <c r="K89" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>36888</v>
+        <v>41981</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.12131678616517</v>
+        <v>0.01044600091462681</v>
       </c>
       <c r="E90" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F90" t="n">
-        <v>35470</v>
+        <v>47895</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.2644893727319855</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>1120</v>
+        <v>2919</v>
       </c>
       <c r="K90" t="n">
-        <v>1527</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>37192</v>
+        <v>36888</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.008241162437649101</v>
+        <v>-0.12131678616517</v>
       </c>
       <c r="E91" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F91" t="n">
-        <v>45049</v>
+        <v>35470</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -43830,32 +44237,32 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.2700592049619397</v>
+        <v>-0.2644893727319855</v>
       </c>
       <c r="J91" t="n">
-        <v>2497</v>
+        <v>1120</v>
       </c>
       <c r="K91" t="n">
-        <v>178</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>39627</v>
+        <v>37192</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.06547106904710691</v>
+        <v>0.008241162437649101</v>
       </c>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F92" t="n">
         <v>45049</v>
@@ -43867,32 +44274,32 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.2700592049619397</v>
       </c>
       <c r="J92" t="n">
-        <v>2686</v>
+        <v>2497</v>
       </c>
       <c r="K92" t="n">
-        <v>34</v>
+        <v>178</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>39858</v>
+        <v>39627</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.005829358770535241</v>
+        <v>0.06547106904710691</v>
       </c>
       <c r="E93" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F93" t="n">
         <v>45049</v>
@@ -43907,29 +44314,29 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>2733</v>
+        <v>2686</v>
       </c>
       <c r="K93" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>41547</v>
+        <v>39858</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.04237543278639169</v>
+        <v>0.005829358770535241</v>
       </c>
       <c r="E94" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F94" t="n">
         <v>45049</v>
@@ -43944,16 +44351,16 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>2689</v>
+        <v>2733</v>
       </c>
       <c r="K94" t="n">
-        <v>126</v>
+        <v>36</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -43963,13 +44370,13 @@
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0</v>
+        <v>0.04237543278639169</v>
       </c>
       <c r="E95" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F95" t="n">
-        <v>48225</v>
+        <v>45049</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -43978,71 +44385,108 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.070501010011321</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>2852</v>
+        <v>2689</v>
       </c>
       <c r="K95" t="n">
-        <v>20</v>
+        <v>126</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>41547</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>23</v>
+      </c>
+      <c r="F96" t="n">
+        <v>48225</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0.070501010011321</v>
+      </c>
+      <c r="J96" t="n">
+        <v>2852</v>
+      </c>
+      <c r="K96" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>41981</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.01044600091462681</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>68</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>47895</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>330</v>
       </c>
-      <c r="I96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="n">
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
         <v>2919</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>5093</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>12425</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>330</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>1799</v>
       </c>
     </row>
@@ -44058,7 +44502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -47094,60 +47538,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>441704</v>
+        <v>541897</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>6373</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.164547002080575</v>
+        <v>0.03701532059769246</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>256860</v>
+        <v>390533</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>26590</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>57091</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.4564246684922694</v>
+        <v>0.003546804701420838</v>
       </c>
       <c r="J82" t="n">
-        <v>35626</v>
+        <v>43817</v>
       </c>
       <c r="K82" t="n">
-        <v>944</v>
+        <v>115</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>460236</v>
+        <v>441704</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.04195569883904153</v>
+        <v>-0.1943677385229905</v>
       </c>
       <c r="E83" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F83" t="n">
-        <v>322027</v>
+        <v>256860</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -47156,13 +47600,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.2537062991512886</v>
+        <v>-0.4583458101194819</v>
       </c>
       <c r="J83" t="n">
-        <v>37062</v>
+        <v>35626</v>
       </c>
       <c r="K83" t="n">
-        <v>133</v>
+        <v>944</v>
       </c>
     </row>
     <row r="84">
@@ -47178,7 +47622,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.04195569883904153</v>
       </c>
       <c r="E84" t="n">
         <v>27</v>
@@ -47193,7 +47637,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>0.2537062991512886</v>
       </c>
       <c r="J84" t="n">
         <v>37062</v>
@@ -47205,23 +47649,23 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>479332</v>
+        <v>460236</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.0414917564032366</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F85" t="n">
-        <v>391685</v>
+        <v>322027</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -47230,35 +47674,35 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.2163110546631183</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>38099</v>
+        <v>37062</v>
       </c>
       <c r="K85" t="n">
-        <v>4</v>
+        <v>133</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>480600</v>
+        <v>479332</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.002645348109452321</v>
+        <v>0.0414917564032366</v>
       </c>
       <c r="E86" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F86" t="n">
-        <v>322524</v>
+        <v>391685</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -47267,35 +47711,35 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>-0.1765730114760586</v>
+        <v>0.2163110546631183</v>
       </c>
       <c r="J86" t="n">
-        <v>39031</v>
+        <v>38099</v>
       </c>
       <c r="K86" t="n">
-        <v>143</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>472805</v>
+        <v>480600</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-0.01621930919683729</v>
+        <v>0.002645348109452321</v>
       </c>
       <c r="E87" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F87" t="n">
-        <v>322739</v>
+        <v>322524</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -47304,35 +47748,35 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.0006666170579553769</v>
+        <v>-0.1765730114760586</v>
       </c>
       <c r="J87" t="n">
-        <v>39534</v>
+        <v>39031</v>
       </c>
       <c r="K87" t="n">
-        <v>208</v>
+        <v>143</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>520910</v>
+        <v>472805</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.1017438478865494</v>
+        <v>-0.01621930919683729</v>
       </c>
       <c r="E88" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F88" t="n">
-        <v>416543</v>
+        <v>322739</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -47341,109 +47785,109 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.2906497200524263</v>
+        <v>0.0006666170579553769</v>
       </c>
       <c r="J88" t="n">
-        <v>40722</v>
+        <v>39534</v>
       </c>
       <c r="K88" t="n">
-        <v>460</v>
+        <v>208</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>528700</v>
+        <v>520910</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.01495459868307385</v>
+        <v>0.1017438478865494</v>
       </c>
       <c r="E89" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="F89" t="n">
-        <v>390533</v>
+        <v>416543</v>
       </c>
       <c r="G89" t="n">
-        <v>26590</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>58303</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.1413611559910982</v>
+        <v>0.2906497200524263</v>
       </c>
       <c r="J89" t="n">
-        <v>42340</v>
+        <v>40722</v>
       </c>
       <c r="K89" t="n">
-        <v>403</v>
+        <v>460</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>441704</v>
+        <v>528700</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.164547002080575</v>
+        <v>0.01495459868307385</v>
       </c>
       <c r="E90" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F90" t="n">
-        <v>256860</v>
+        <v>390533</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>26590</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>58303</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.4597266451561337</v>
+        <v>0.1413611559910982</v>
       </c>
       <c r="J90" t="n">
-        <v>35626</v>
+        <v>42340</v>
       </c>
       <c r="K90" t="n">
-        <v>944</v>
+        <v>403</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>464766</v>
+        <v>441704</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.05221143571260391</v>
+        <v>-0.164547002080575</v>
       </c>
       <c r="E91" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F91" t="n">
-        <v>322011</v>
+        <v>256860</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -47452,35 +47896,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.2536440084092502</v>
+        <v>-0.4597266451561337</v>
       </c>
       <c r="J91" t="n">
-        <v>37088</v>
+        <v>35626</v>
       </c>
       <c r="K91" t="n">
-        <v>83</v>
+        <v>944</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>480181</v>
+        <v>464766</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.03316722823958723</v>
+        <v>0.05221143571260391</v>
       </c>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F92" t="n">
-        <v>391685</v>
+        <v>322011</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -47489,35 +47933,35 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.2163714904149237</v>
+        <v>0.2536440084092502</v>
       </c>
       <c r="J92" t="n">
-        <v>38154</v>
+        <v>37088</v>
       </c>
       <c r="K92" t="n">
-        <v>14</v>
+        <v>83</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>480600</v>
+        <v>480181</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.0008725876284151184</v>
+        <v>0.03316722823958723</v>
       </c>
       <c r="E93" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F93" t="n">
-        <v>322524</v>
+        <v>391685</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -47526,35 +47970,35 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>-0.1765730114760586</v>
+        <v>0.2163714904149237</v>
       </c>
       <c r="J93" t="n">
-        <v>39050</v>
+        <v>38154</v>
       </c>
       <c r="K93" t="n">
-        <v>154</v>
+        <v>14</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>472805</v>
+        <v>480600</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>-0.01621930919683729</v>
+        <v>0.0008725876284151184</v>
       </c>
       <c r="E94" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F94" t="n">
-        <v>322739</v>
+        <v>322524</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -47563,35 +48007,35 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.0006666170579553769</v>
+        <v>-0.1765730114760586</v>
       </c>
       <c r="J94" t="n">
-        <v>39541</v>
+        <v>39050</v>
       </c>
       <c r="K94" t="n">
-        <v>271</v>
+        <v>154</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>523323</v>
+        <v>472805</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.1068474318164994</v>
+        <v>-0.01621930919683729</v>
       </c>
       <c r="E95" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F95" t="n">
-        <v>416543</v>
+        <v>322739</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -47600,71 +48044,108 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.2906497200524263</v>
+        <v>0.0006666170579553769</v>
       </c>
       <c r="J95" t="n">
-        <v>41304</v>
+        <v>39541</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>271</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>523323</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.1068474318164994</v>
+      </c>
+      <c r="E96" t="n">
+        <v>23</v>
+      </c>
+      <c r="F96" t="n">
+        <v>416543</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0.2906497200524263</v>
+      </c>
+      <c r="J96" t="n">
+        <v>41304</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>528700</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.01027472516973265</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>68</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>390533</v>
       </c>
-      <c r="G96" t="n">
+      <c r="G97" t="n">
         <v>26590</v>
       </c>
-      <c r="H96" t="n">
+      <c r="H97" t="n">
         <v>58303</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.1413611559910982</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>42340</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>489</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>86531</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>133673</v>
       </c>
-      <c r="G97" s="4" t="n">
+      <c r="G98" s="4" t="n">
         <v>26590</v>
       </c>
-      <c r="H97" s="4" t="n">
+      <c r="H98" s="4" t="n">
         <v>58303</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>6692</v>
       </c>
     </row>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4333,7 +4333,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>156168</v>
@@ -4351,7 +4351,7 @@
         <v>14115</v>
       </c>
       <c r="K82" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="83">
@@ -7992,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -8010,7 +8010,7 @@
         <v>1817</v>
       </c>
       <c r="K82" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="83">
@@ -11651,7 +11651,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -14681,7 +14681,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -18266,7 +18266,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -21938,7 +21938,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>37421</v>
@@ -25597,7 +25597,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>35588</v>
@@ -29256,7 +29256,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -32915,7 +32915,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>52024</v>
@@ -36574,7 +36574,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>30655</v>
@@ -40233,7 +40233,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -43892,7 +43892,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>47895</v>
@@ -43910,7 +43910,7 @@
         <v>2976</v>
       </c>
       <c r="K82" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="83">
@@ -47551,7 +47551,7 @@
         <v>0.03701532059769246</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>390533</v>
@@ -47569,7 +47569,7 @@
         <v>43817</v>
       </c>
       <c r="K82" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4333,7 +4333,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>156168</v>
@@ -7992,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -11651,7 +11651,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -14681,7 +14681,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -18266,7 +18266,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -21938,7 +21938,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>37421</v>
@@ -25597,7 +25597,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>35588</v>
@@ -29256,7 +29256,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -32915,7 +32915,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>52024</v>
@@ -36574,7 +36574,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>30655</v>
@@ -40233,7 +40233,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -43892,7 +43892,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>47895</v>
@@ -47551,7 +47551,7 @@
         <v>0.03701532059769246</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>390533</v>
@@ -47566,10 +47566,10 @@
         <v>0.003546804701420838</v>
       </c>
       <c r="J82" t="n">
-        <v>43817</v>
+        <v>43929</v>
       </c>
       <c r="K82" t="n">
-        <v>113</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4333,7 +4333,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>156168</v>
@@ -7992,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -11651,7 +11651,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -14681,7 +14681,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -18266,7 +18266,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -21938,7 +21938,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>37421</v>
@@ -25597,7 +25597,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>35588</v>
@@ -29256,7 +29256,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -32915,7 +32915,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>52024</v>
@@ -36574,7 +36574,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>30655</v>
@@ -40233,7 +40233,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -43892,7 +43892,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>47895</v>
@@ -47551,7 +47551,7 @@
         <v>0.03701532059769246</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>390533</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4333,7 +4333,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>156168</v>
@@ -7992,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -11651,7 +11651,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -14681,7 +14681,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -18266,7 +18266,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -21938,7 +21938,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>37421</v>
@@ -25597,7 +25597,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>35588</v>
@@ -29256,7 +29256,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -32915,7 +32915,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>52024</v>
@@ -36574,7 +36574,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>30655</v>
@@ -40233,7 +40233,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -43892,7 +43892,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>47895</v>
@@ -47551,7 +47551,7 @@
         <v>0.03701532059769246</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>390533</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4351,7 +4351,7 @@
         <v>14115</v>
       </c>
       <c r="K82" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="83">
@@ -36592,7 +36592,7 @@
         <v>1717</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -47569,7 +47569,7 @@
         <v>43929</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4333,7 +4333,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>156168</v>
@@ -4351,7 +4351,7 @@
         <v>14115</v>
       </c>
       <c r="K82" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="83">
@@ -7992,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -11651,7 +11651,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -14681,7 +14681,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -18266,7 +18266,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -21938,7 +21938,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>37421</v>
@@ -25597,7 +25597,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>35588</v>
@@ -29256,7 +29256,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -32915,7 +32915,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>52024</v>
@@ -36574,7 +36574,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>30655</v>
@@ -36592,7 +36592,7 @@
         <v>1717</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -40233,7 +40233,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -43892,7 +43892,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>47895</v>
@@ -47551,7 +47551,7 @@
         <v>0.03701532059769246</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>390533</v>
@@ -47569,7 +47569,7 @@
         <v>43929</v>
       </c>
       <c r="K82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -8010,7 +8010,7 @@
         <v>1817</v>
       </c>
       <c r="K82" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="83">
@@ -21956,7 +21956,7 @@
         <v>3688</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4351,7 +4351,7 @@
         <v>14115</v>
       </c>
       <c r="K82" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="83">
@@ -36592,7 +36592,7 @@
         <v>1717</v>
       </c>
       <c r="K82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -47569,7 +47569,7 @@
         <v>43929</v>
       </c>
       <c r="K82" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4351,7 +4351,7 @@
         <v>14115</v>
       </c>
       <c r="K82" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="83">
@@ -47569,7 +47569,7 @@
         <v>43929</v>
       </c>
       <c r="K82" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4351,7 +4351,7 @@
         <v>14115</v>
       </c>
       <c r="K82" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="83">
@@ -21956,7 +21956,7 @@
         <v>3688</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -32933,7 +32933,7 @@
         <v>4566</v>
       </c>
       <c r="K82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83">
@@ -47569,7 +47569,7 @@
         <v>43929</v>
       </c>
       <c r="K82" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4351,7 +4351,7 @@
         <v>14115</v>
       </c>
       <c r="K82" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="83">
@@ -21956,7 +21956,7 @@
         <v>3688</v>
       </c>
       <c r="K82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -25615,7 +25615,7 @@
         <v>2620</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -32933,7 +32933,7 @@
         <v>4566</v>
       </c>
       <c r="K82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83">
@@ -47569,7 +47569,7 @@
         <v>43929</v>
       </c>
       <c r="K82" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4351,7 +4351,7 @@
         <v>14115</v>
       </c>
       <c r="K82" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="83">
@@ -43910,7 +43910,7 @@
         <v>2976</v>
       </c>
       <c r="K82" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="83">
@@ -47569,7 +47569,7 @@
         <v>43929</v>
       </c>
       <c r="K82" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -32933,7 +32933,7 @@
         <v>4566</v>
       </c>
       <c r="K82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
@@ -47569,7 +47569,7 @@
         <v>43929</v>
       </c>
       <c r="K82" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -14699,7 +14699,7 @@
         <v>241</v>
       </c>
       <c r="K65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66">
@@ -47569,7 +47569,7 @@
         <v>43929</v>
       </c>
       <c r="K82" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4333,7 +4333,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>156168</v>
@@ -4351,7 +4351,7 @@
         <v>14115</v>
       </c>
       <c r="K82" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="83">
@@ -7992,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -11651,7 +11651,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -14681,7 +14681,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -18266,7 +18266,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -21938,7 +21938,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>37421</v>
@@ -25597,7 +25597,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>35588</v>
@@ -29256,7 +29256,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -32915,7 +32915,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>52024</v>
@@ -32933,7 +32933,7 @@
         <v>4566</v>
       </c>
       <c r="K82" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="83">
@@ -36574,7 +36574,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>30655</v>
@@ -40233,7 +40233,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -43892,7 +43892,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>47895</v>
@@ -43910,7 +43910,7 @@
         <v>2976</v>
       </c>
       <c r="K82" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="83">
@@ -47551,7 +47551,7 @@
         <v>0.03701532059769246</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>390533</v>
@@ -47569,7 +47569,7 @@
         <v>43929</v>
       </c>
       <c r="K82" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4351,7 +4351,7 @@
         <v>14115</v>
       </c>
       <c r="K82" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="83">
@@ -47569,7 +47569,7 @@
         <v>43929</v>
       </c>
       <c r="K82" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4333,7 +4333,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>156168</v>
@@ -4351,7 +4351,7 @@
         <v>14115</v>
       </c>
       <c r="K82" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="83">
@@ -7992,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -11651,7 +11651,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -14681,7 +14681,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -18266,7 +18266,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -21938,7 +21938,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>37421</v>
@@ -25597,7 +25597,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>35588</v>
@@ -29256,7 +29256,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -32915,7 +32915,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>52024</v>
@@ -36574,7 +36574,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>30655</v>
@@ -40233,7 +40233,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -43892,7 +43892,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>47895</v>
@@ -47551,7 +47551,7 @@
         <v>0.03701532059769246</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>390533</v>
@@ -47569,7 +47569,7 @@
         <v>43929</v>
       </c>
       <c r="K82" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4333,7 +4333,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>156168</v>
@@ -4348,10 +4348,10 @@
         <v>0.01819581627671161</v>
       </c>
       <c r="J82" t="n">
-        <v>14115</v>
+        <v>14182</v>
       </c>
       <c r="K82" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -7992,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -11651,7 +11651,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -14681,7 +14681,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -18266,7 +18266,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -21938,7 +21938,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>37421</v>
@@ -25597,7 +25597,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>35588</v>
@@ -29256,7 +29256,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -32906,16 +32906,16 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>72396</v>
+        <v>73767</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0</v>
+        <v>0.01893751035968838</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>52024</v>
@@ -32933,7 +32933,7 @@
         <v>4566</v>
       </c>
       <c r="K82" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83">
@@ -32949,7 +32949,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.2180507210343113</v>
+        <v>-0.232583675627313</v>
       </c>
       <c r="E83" t="n">
         <v>18</v>
@@ -36574,7 +36574,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>30655</v>
@@ -40233,7 +40233,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -43892,7 +43892,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>47895</v>
@@ -47551,7 +47551,7 @@
         <v>0.03701532059769246</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>390533</v>
@@ -47569,7 +47569,7 @@
         <v>43929</v>
       </c>
       <c r="K82" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4351,7 +4351,7 @@
         <v>14182</v>
       </c>
       <c r="K82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
@@ -32933,7 +32933,7 @@
         <v>4566</v>
       </c>
       <c r="K82" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83">
@@ -43910,7 +43910,7 @@
         <v>2976</v>
       </c>
       <c r="K82" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="83">
@@ -47569,7 +47569,7 @@
         <v>43929</v>
       </c>
       <c r="K82" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4333,7 +4333,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>156168</v>
@@ -4351,7 +4351,7 @@
         <v>14182</v>
       </c>
       <c r="K82" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="83">
@@ -7992,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -11651,7 +11651,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -14681,7 +14681,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -18266,7 +18266,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -21938,7 +21938,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>37421</v>
@@ -25597,7 +25597,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>35588</v>
@@ -29256,7 +29256,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -32915,7 +32915,7 @@
         <v>0.01893751035968838</v>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>52024</v>
@@ -36574,7 +36574,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>30655</v>
@@ -40233,7 +40233,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -43892,7 +43892,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>47895</v>
@@ -43910,7 +43910,7 @@
         <v>2976</v>
       </c>
       <c r="K82" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="83">
@@ -47551,25 +47551,25 @@
         <v>0.03701532059769246</v>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
-        <v>390533</v>
+        <v>413106</v>
       </c>
       <c r="G82" t="n">
         <v>26590</v>
       </c>
       <c r="H82" t="n">
-        <v>57091</v>
+        <v>58364</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.003546804701420838</v>
+        <v>0.0540104711155505</v>
       </c>
       <c r="J82" t="n">
         <v>43929</v>
       </c>
       <c r="K82" t="n">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
     <row r="83">
@@ -47600,7 +47600,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>-0.4583458101194819</v>
+        <v>-0.4842790025298157</v>
       </c>
       <c r="J83" t="n">
         <v>35626</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4333,7 +4333,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F82" t="n">
         <v>156168</v>
@@ -4351,7 +4351,7 @@
         <v>14182</v>
       </c>
       <c r="K82" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83">
@@ -7992,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -11651,7 +11651,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -14681,7 +14681,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -18266,7 +18266,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -21938,7 +21938,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F82" t="n">
         <v>37421</v>
@@ -25597,7 +25597,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F82" t="n">
         <v>35588</v>
@@ -29256,7 +29256,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -32915,7 +32915,7 @@
         <v>0.01893751035968838</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F82" t="n">
         <v>52024</v>
@@ -32933,7 +32933,7 @@
         <v>4566</v>
       </c>
       <c r="K82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83">
@@ -36574,7 +36574,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F82" t="n">
         <v>30655</v>
@@ -40233,7 +40233,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -43892,7 +43892,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F82" t="n">
         <v>47895</v>
@@ -43910,7 +43910,7 @@
         <v>2976</v>
       </c>
       <c r="K82" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="83">
@@ -47551,7 +47551,7 @@
         <v>0.03701532059769246</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F82" t="n">
         <v>413106</v>
@@ -47569,7 +47569,7 @@
         <v>43929</v>
       </c>
       <c r="K82" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4333,7 +4333,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F82" t="n">
         <v>156168</v>
@@ -4351,7 +4351,7 @@
         <v>14182</v>
       </c>
       <c r="K82" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83">
@@ -7992,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -11651,7 +11651,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -14681,7 +14681,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -18266,7 +18266,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -21938,7 +21938,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F82" t="n">
         <v>37421</v>
@@ -25597,7 +25597,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F82" t="n">
         <v>35588</v>
@@ -29256,7 +29256,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -32915,7 +32915,7 @@
         <v>0.01893751035968838</v>
       </c>
       <c r="E82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F82" t="n">
         <v>52024</v>
@@ -36574,7 +36574,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F82" t="n">
         <v>30655</v>
@@ -40233,7 +40233,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -43892,7 +43892,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F82" t="n">
         <v>47895</v>
@@ -47551,7 +47551,7 @@
         <v>0.03701532059769246</v>
       </c>
       <c r="E82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F82" t="n">
         <v>413106</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -47566,10 +47566,10 @@
         <v>0.0540104711155505</v>
       </c>
       <c r="J82" t="n">
-        <v>43929</v>
+        <v>44008</v>
       </c>
       <c r="K82" t="n">
-        <v>119</v>
+        <v>40</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4333,7 +4333,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E82" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>156168</v>
@@ -7992,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -11651,7 +11651,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -14681,7 +14681,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -18266,7 +18266,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -21938,7 +21938,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>37421</v>
@@ -25597,7 +25597,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>35588</v>
@@ -29256,7 +29256,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -32915,7 +32915,7 @@
         <v>0.01893751035968838</v>
       </c>
       <c r="E82" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>52024</v>
@@ -36574,7 +36574,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>30655</v>
@@ -40233,7 +40233,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -43892,7 +43892,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>47895</v>
@@ -47551,7 +47551,7 @@
         <v>0.03701532059769246</v>
       </c>
       <c r="E82" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>413106</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -4333,7 +4333,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F82" t="n">
         <v>156168</v>
@@ -7992,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -11651,7 +11651,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -14681,7 +14681,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -18266,7 +18266,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -21938,7 +21938,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F82" t="n">
         <v>37421</v>
@@ -25597,7 +25597,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F82" t="n">
         <v>35588</v>
@@ -29256,7 +29256,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -32915,7 +32915,7 @@
         <v>0.01893751035968838</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F82" t="n">
         <v>52024</v>
@@ -36574,7 +36574,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F82" t="n">
         <v>30655</v>
@@ -40233,7 +40233,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -43892,7 +43892,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F82" t="n">
         <v>47895</v>
@@ -47551,7 +47551,7 @@
         <v>0.03701532059769246</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F82" t="n">
         <v>413106</v>
